--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t>Status der Allergie; active | inactive | resolved</t>
+    <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -573,7 +573,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>ToDo; Presumed, gibt es hierzu aktuelle Infos? kardinalität von clinicalStatus &amp; verificationStatus muss noch erarbeitet werden. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -598,7 +598,7 @@
 Class</t>
   </si>
   <si>
-    <t>Identifikation ob es eine Allergie oder Intoleranz ist</t>
+    <t>Kennzeichnung, ob es sich um eine Allergie oder Intoleranz handelt.</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -629,7 +629,7 @@
 TypeReaction TypeClass</t>
   </si>
   <si>
-    <t>Differenzierung nach Kontext - Medikamente, Lebensmittel, Umwelt,.. - falls nur med. rele. dann ist es nicht notwendig, fachlich klären</t>
+    <t>ToDo - falls nur med. rele. dann ist es nicht notwendig, fachlich klären: Differenzierung nach Kontext z. B. Medikamente, Lebensmittel oder Umwelt.</t>
   </si>
   <si>
     <t>Category of the identified substance.</t>
@@ -657,7 +657,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>Einschätzung der Schwere (Anaphylaxie)</t>
+    <t>Einschätzung des Schweregrads, z. B. im Hinblick auf eine Anaphylaxie.</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -688,7 +688,7 @@
 </t>
   </si>
   <si>
-    <t>Allergiecode, Text verboten</t>
+    <t>Allergiecode; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -826,7 +826,7 @@
 </t>
   </si>
   <si>
-    <t>Betroffene Person, auf die sich die Allergie bezieht</t>
+    <t>Betroffene Person, auf die sich die Allergie bezieht.</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -848,7 +848,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The encounter when the allergy or intolerance was asserted.</t>
@@ -867,7 +867,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>Erstes Aufzeichnungsdatum der Allergie(symptomatik)</t>
+    <t>Erstes Aufzeichnungsdatum der Allergie bzw. Allergiesymptomatik.</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -886,7 +886,7 @@
 </t>
   </si>
   <si>
-    <t>Dokumentationsdatum</t>
+    <t>Dokumentationsdatum.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -912,7 +912,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, die die Allergie ins System erfasst/dokumentiert</t>
+    <t>GDA, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -935,7 +935,7 @@
 </t>
   </si>
   <si>
-    <t>Person (fachliche Quelle + related Person oder Patient selbst), die/der die Allergie bestätigt</t>
+    <t>Quelle der Information zur Allergie, z. B. Patient, behandelnde Person oder Dritter.</t>
   </si>
   <si>
     <t>The source of the information about the allergy that is recorded.</t>
@@ -956,7 +956,7 @@
     <t>AllergyIntolerance.lastOccurrence</t>
   </si>
   <si>
-    <t>Letztes Auftreten der Symptomatik - siehe manifestation</t>
+    <t>Letztes Auftreten der Symptomatik; siehe Manifestation.</t>
   </si>
   <si>
     <t>Represents the date and/or time of the last known occurrence of a reaction event.</t>
@@ -975,7 +975,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen oder Freitext zur Allergie wird in reaction beschrieben</t>
+    <t>Zusätzliche Informationen; Freitext wird in reaction beschrieben.</t>
   </si>
   <si>
     <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
@@ -994,7 +994,7 @@
 </t>
   </si>
   <si>
-    <t>Details über die Allergiereaktion</t>
+    <t>Details zur allergischen Reaktion.</t>
   </si>
   <si>
     <t>Details about each adverse reaction event linked to exposure to the identified substance.</t>
@@ -1019,7 +1019,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitlicher Verlauf der Manifestation</t>
+    <t>Zeitlicher Verlauf der Manifestation.</t>
   </si>
   <si>
     <t>Zeitlicher Verlauf der Manifestation (&lt;6h, 6-24h, &gt;24h, unknown)</t>
@@ -1045,7 +1045,7 @@
     <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
-    <t>Spezifische Substanz die zur Allergie führt, wird in allergyintoleranz.code gelöst</t>
+    <t>Spezifische Substanz, die zur Allergie führt; wird über AllergyIntolerance.code abgebildet.</t>
   </si>
   <si>
     <t>Identification of the specific substance (or pharmaceutical product) considered to be responsible for the Adverse Reaction event. Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -1070,7 +1070,7 @@
 Signs</t>
   </si>
   <si>
-    <t>Aufgezeichnete klinische allergische Symptome</t>
+    <t>Aufgezeichnete klinische Symptome der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
@@ -1095,7 +1095,7 @@
 Text</t>
   </si>
   <si>
-    <t>Textbasierte Zusammenfassung der allergischen Reaktion</t>
+    <t>Textbasierte Zusammenfassung der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Text description about the reaction as a whole, including details of the manifestation if required.</t>
@@ -1110,7 +1110,7 @@
     <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
-    <t>Beginn der Reaktion</t>
+    <t>Beginn der Reaktion.</t>
   </si>
   <si>
     <t>Record of the date and/or time of the onset of the Reaction.</t>
@@ -1122,7 +1122,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>Beschreibt ob die Reaktion mild, moderat,... war</t>
+    <t>Schweregrad der Reaktion, z. B. mild oder moderat.</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -1140,7 +1140,7 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>Art der Exposition der betroffenen Person gegenüber der Substanz</t>
+    <t>Art der Exposition der betroffenen Person gegenüber der Substanz.</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.</t>
@@ -1161,7 +1161,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>
